--- a/daily_matches/job_matches_2026-05-18.xlsx
+++ b/daily_matches/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Agentic AI - Python Expert</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M-TECH SYSTEMS</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, MLflow, FastAPI, AKS, CI/CD, Git, Databricks</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0c27160d37deec</t>
+          <t>https://www.indeed.com/viewjob?jk=2f5602fabde512ac</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Applied AI</t>
+          <t>Hadoop Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,77 +531,322 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8a6b1a80e94746</t>
+          <t>https://www.indeed.com/viewjob?jk=9772886a5282fba2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Solutions Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Apache Airflow, CI/CD, Terraform, Git, Python, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b7f11613741a49</t>
+          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>App Software &amp; AI Engineer, Advisor</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Southern California Edison</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rosemead, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=870c831c3d1ab7ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Applied AI ML Engineer-Senior Associate</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=126d85a333193194</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Presentation and Visual Optimization</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Paramount Streaming</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bb2ee0f5051de55</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer, Connectors Framework</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexla</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>California City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Snowflake, Databricks, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c609559a48fe285a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nesa Software Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, AWS SageMaker, Glue, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a91281e2ae9d3b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (SF/On-site)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Soulside AI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, EC2, Kinesis, AKS, Terraform, Kafka, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be7ef0350aec31bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a20839901f19a8b</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=228cc3ab331c7326</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Helixtachinc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dallas, WV, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56bd9fdd257c9a9d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-18.xlsx
+++ b/daily_matches/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>Full-Stack Weather Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>11.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Dask, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f5602fabde512ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1bb6619a7b36f9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hadoop Developer</t>
+          <t>VIE - Data Scientist - Analytics &amp; IA Générative - H/F</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Saint-Gobain</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Kubernetes, CI/CD, Snowflake, Databricks, BigQuery, Kafka, Hadoop</t>
+          <t>Data Scientist, RAG, Copilot, TensorFlow, Git, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9772886a5282fba2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca2b97bc71cac8db</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>AI Engineer, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af679155705e54bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee17b8e36fc7f358</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior PHP Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gravity Lending</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, CI/CD, PostgreSQL, Python, SQL</t>
+          <t>Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,252 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=870c831c3d1ab7ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Applied AI ML Engineer-Senior Associate</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=126d85a333193194</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Presentation and Visual Optimization</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Paramount Streaming</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bb2ee0f5051de55</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Software Engineer, Connectors Framework</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Nexla</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>California City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, Snowflake, Databricks, Kafka, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c609559a48fe285a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nesa Software Pvt Ltd</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, AWS SageMaker, Glue, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a91281e2ae9d3b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer (SF/On-site)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Soulside AI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, EC2, Kinesis, AKS, Terraform, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-05-17</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be7ef0350aec31bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Fullstack Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=228cc3ab331c7326</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Helixtachinc</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Dallas, WV, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56bd9fdd257c9a9d</t>
+          <t>https://www.indeed.com/viewjob?jk=a94dec3cd6d6cf67</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-18.xlsx
+++ b/daily_matches/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack Weather Software Engineer</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Dask, Python, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, MLflow, CI/CD, Databricks, PySpark, Hadoop, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1bb6619a7b36f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VIE - Data Scientist - Analytics &amp; IA Générative - H/F</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Saint-Gobain</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, TensorFlow, Git, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Redshift, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca2b97bc71cac8db</t>
+          <t>https://www.indeed.com/viewjob?jk=9df1a1fdaf701a58</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward Deployment Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, PyTorch, GCP Vertex AI, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,532 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee17b8e36fc7f358</t>
+          <t>https://www.indeed.com/viewjob?jk=f8743e2d3e24ea2b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior PHP Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gravity Lending</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae2dcef05bbeedb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marketing Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Terpene Belt Inc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, Prompt Engineering, BigQuery, Git, Snowflake, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a926efa78b896610</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cloud Data Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Amway</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ada, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Kafka, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The Standard Insurance</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=034376f4289a38c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OnMed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>White Plains, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mimecast</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33f61fe9a0d87048</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SUPPLIER.IO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62fecc0c2154e4b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IntegriChain</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arizent</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14c4d570afb24aab</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Arizent</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=86514318033dc541</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Docker, CI/CD, GitHub Actions, Git, MySQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a94dec3cd6d6cf67</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Backend</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Commerce</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27db66f761d7692b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alphanumeric Systems Inc</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, PySpark, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aafc1066893dd26c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst, Marketing Analytics</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>freshworks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Data Lake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d7aac29b25488fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Associate CloudOps Engineer -- Muscatek, Inc. Remote (United States) | Contract to Hire</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Muscatek, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=868abf5dfc03e51c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-18.xlsx
+++ b/daily_matches/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data and Insight Analyst</t>
+          <t>ECG / TCU Product Development Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, MLflow, CI/CD, Databricks, PySpark, Hadoop, PostgreSQL</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery, MLflow, CI/CD, Git, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb46af131203645d</t>
+          <t>https://www.indeed.com/viewjob?jk=a70538c48f0435bc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>Pax8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Redshift, FastAPI, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Athena, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9df1a1fdaf701a58</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Forward Deployment Engineer (Generative AI)</t>
+          <t>Senior Software Engineer â€“ Application Reliability , Hybrid</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, PyTorch, GCP Vertex AI, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Kubernetes, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8743e2d3e24ea2b</t>
+          <t>https://www.indeed.com/viewjob?jk=561b5decdba479cc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sales Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>Cube Dev</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, Snowflake, Databricks, Python</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae2dcef05bbeedb2</t>
+          <t>https://www.indeed.com/viewjob?jk=9bde282e8e25b694</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marketing Engineer</t>
+          <t>AI Agent Builder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Terpene Belt Inc</t>
+          <t>Mirakl - Labs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Prompt Engineering, BigQuery, Git, Snowflake, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Mistral, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a926efa78b896610</t>
+          <t>https://www.indeed.com/viewjob?jk=09617fc34de9127b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, BigQuery, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2e59f6a4d8593c</t>
+          <t>https://www.indeed.com/viewjob?jk=69fbc1dd23d22baa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer III, Data Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Standard Insurance</t>
+          <t>Agility Robotics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, FastAPI, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
+          <t>RAG, S3, Athena, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034376f4289a38c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a69c08bba0b59de0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer III, Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OnMed</t>
+          <t>Agility Robotics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>RAG, S3, Athena, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15fa432a086d4c1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8878c45239111930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Software Engineer III, Data Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mimecast</t>
+          <t>Agility Robotics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Glue, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
+          <t>RAG, S3, Athena, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f61fe9a0d87048</t>
+          <t>https://www.indeed.com/viewjob?jk=c33d3e6d06fef435</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SUPPLIER.IO</t>
+          <t>Round 2 Ai, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stuart, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Git, Snowflake, Python, SQL, R</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62fecc0c2154e4b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e7b37513a519444</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr AI Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IntegriChain</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,252 +846,42 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28193f1af5326eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Arizent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, CI/CD, Git, Kafka, Hadoop, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c4d570afb24aab</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data &amp; AI Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Arizent</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86514318033dc541</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Databricks, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa2e0e889ce30184</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Backend</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Commerce</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27db66f761d7692b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Alphanumeric Systems Inc</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, PySpark, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aafc1066893dd26c</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst, Marketing Analytics</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>freshworks</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Data Lake, Databricks, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7aac29b25488fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Associate CloudOps Engineer -- Muscatek, Inc. Remote (United States) | Contract to Hire</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Muscatek, Inc.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>S3, EC2, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=868abf5dfc03e51c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9aca5de364cc4e6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-05-18.xlsx
+++ b/daily_matches/job_matches_2026-05-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ECG / TCU Product Development Engineer</t>
+          <t>Sr. GenAI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>XomegaIT Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery, MLflow, CI/CD, Git, BigQuery</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70538c48f0435bc</t>
+          <t>https://www.indeed.com/viewjob?jk=13b5c664f0411250</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Engineer/ Sr Engineer, IT AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pax8</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Athena, Redshift, BigQuery, Docker, Kubernetes, CI/CD, Terraform, BigQuery, Redshift</t>
+          <t>Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb9ce5f60166ab4</t>
+          <t>https://www.indeed.com/viewjob?jk=8163f05597e70026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer â€“ Application Reliability , Hybrid</t>
+          <t>Sr. Engineer AI/Agentic</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Lendistry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, BigQuery, Kubernetes, Git, BigQuery, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=561b5decdba479cc</t>
+          <t>https://www.indeed.com/viewjob?jk=39eba20fd30e1c72</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sales Engineer</t>
+          <t>Data Engineer - Active TS/SCI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cube Dev</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>S3, Redshift, Dataflow, Docker, Kubernetes, Git, Redshift, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bde282e8e25b694</t>
+          <t>https://www.indeed.com/viewjob?jk=f872fe833e94e41d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Agent Builder</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mirakl - Labs</t>
+          <t>Bamboo Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Gemini, Mistral, Git, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09617fc34de9127b</t>
+          <t>https://www.indeed.com/viewjob?jk=de8ea03efdc31e4c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69fbc1dd23d22baa</t>
+          <t>https://www.indeed.com/viewjob?jk=826018c1b43a8cf3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Agility Robotics</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>Copilot, S3, Glue, Redshift, CI/CD, Terraform, Git, Redshift, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69c08bba0b59de0</t>
+          <t>https://www.indeed.com/viewjob?jk=69eacc98e74b3522</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agility Robotics</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8878c45239111930</t>
+          <t>https://www.indeed.com/viewjob?jk=6fff5dba4d6db08c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III, Data Platform</t>
+          <t>Senior Software Engineer - Business Operations &amp; Automation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Agility Robotics</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Kubernetes, Kafka, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c33d3e6d06fef435</t>
+          <t>https://www.indeed.com/viewjob?jk=bf30e5f6ab93a210</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer - Business Operations &amp; Automation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Round 2 Ai, LLC</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stuart, FL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e7b37513a519444</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ef17c22c1e9d3b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr AI Data Engineer</t>
+          <t>Senior Software Engineer - Business Operations &amp; Automation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, Glue, Athena, Git, Python, SQL, R</t>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,392 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002c6cfe2bf32d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2c9505b31a1403d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior Software Engineer - Business Operations &amp; Automation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>SpotOn</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ae3fcb3956948a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MTS Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, EC2, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a7da1c5e3747bb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Engineer - Hybrid in IL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CI/CD, GitHub Actions, Git, Snowflake, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9db02075074ae63</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Agentic AI Developer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Calpion/Plutus Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db5673b338d3cd79</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (Azure / DevOps / AI Infrastructure)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, CI/CD, Git, Kafka, Hadoop, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9aca5de364cc4e6</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba1b967ee4e90a5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Talent Acquisition Specialist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Qode</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Kubernetes, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f564d7d56eefb0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63e5614a44c15b93</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Associate Analytics Engineer - Applied AI &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Murphy Oil Corporation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4500c6a0924af994</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Developer II - Customer Growth</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Kafka, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41abcb51409e2cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RX USA LLC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Souderton, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Databricks, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c6f69adb5e63bee</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Utilities Data Analyst</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MCKIM &amp; CREED</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wilmington, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Power BI, Matplotlib, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=142d059703d2a0df</t>
         </is>
       </c>
     </row>
